--- a/data/shvets_kovalenko_2026.xlsx
+++ b/data/shvets_kovalenko_2026.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30618"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="440">
   <si>
     <t>17 января  2026г.</t>
   </si>
@@ -1219,9 +1219,6 @@
     <t>1,01,47</t>
   </si>
   <si>
-    <t>Шемчук Саша</t>
-  </si>
-  <si>
     <t>0,59,23</t>
   </si>
   <si>
@@ -1352,6 +1349,9 @@
   </si>
   <si>
     <t>Труханов Александр</t>
+  </si>
+  <si>
+    <t>Шемчук Александр</t>
   </si>
 </sst>
 </file>
@@ -2015,13 +2015,13 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2344,24 +2344,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B1" s="122" t="s">
+      <c r="B1" s="123" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="122"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B3" s="2"/>
@@ -5646,24 +5646,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B1" s="123" t="s">
+      <c r="B1" s="124" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B2" s="123" t="s">
+      <c r="B2" s="124" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B3" s="67"/>
@@ -8394,15 +8394,15 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="77"/>
-      <c r="B1" s="124" t="s">
+      <c r="B1" s="122" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="120" t="s">
@@ -8440,7 +8440,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="79" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B5" s="107" t="s">
         <v>1</v>
@@ -8455,7 +8455,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="119" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G5" s="119" t="s">
         <v>4</v>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="E8" s="56"/>
       <c r="F8" s="94" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G8" s="94" t="s">
         <v>347</v>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="E9" s="56"/>
       <c r="F9" s="94" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G9" s="94" t="s">
         <v>347</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="E10" s="56"/>
       <c r="F10" s="94" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G10" s="94" t="s">
         <v>347</v>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="E11" s="56"/>
       <c r="F11" s="94" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G11" s="94" t="s">
         <v>347</v>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="E12" s="56"/>
       <c r="F12" s="94" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G12" s="94" t="s">
         <v>347</v>
@@ -8628,14 +8628,14 @@
         <v>7</v>
       </c>
       <c r="C13" s="117" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D13" s="96">
         <v>2016</v>
       </c>
       <c r="E13" s="56"/>
       <c r="F13" s="94" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G13" s="94" t="s">
         <v>346</v>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E14" s="56"/>
       <c r="F14" s="94" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G14" s="94" t="s">
         <v>346</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="E15" s="56"/>
       <c r="F15" s="94" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G15" s="94" t="s">
         <v>346</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="E16" s="56"/>
       <c r="F16" s="94" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G16" s="94" t="s">
         <v>346</v>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="E17" s="56"/>
       <c r="F17" s="94" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G17" s="94" t="s">
         <v>346</v>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="E18" s="56"/>
       <c r="F18" s="94" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G18" s="94" t="s">
         <v>346</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="E19" s="56"/>
       <c r="F19" s="94" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G19" s="94" t="s">
         <v>346</v>
@@ -8796,14 +8796,14 @@
         <v>14</v>
       </c>
       <c r="C20" s="117" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D20" s="96">
         <v>2016</v>
       </c>
       <c r="E20" s="56"/>
       <c r="F20" s="94" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G20" s="94" t="s">
         <v>346</v>
@@ -8818,14 +8818,14 @@
         <v>15</v>
       </c>
       <c r="C21" s="105" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D21" s="93">
         <v>2017</v>
       </c>
       <c r="E21" s="56"/>
       <c r="F21" s="92" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G21" s="94" t="s">
         <v>346</v>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="E22" s="56"/>
       <c r="F22" s="94" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G22" s="94" t="s">
         <v>346</v>
@@ -8903,10 +8903,10 @@
       </c>
       <c r="E25" s="56"/>
       <c r="F25" s="94" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G25" s="94" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H25" s="95" t="s">
         <v>126</v>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="E26" s="56"/>
       <c r="F26" s="94" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G26" s="94" t="s">
         <v>347</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="E27" s="56"/>
       <c r="F27" s="94" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G27" s="94" t="s">
         <v>346</v>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="E28" s="56"/>
       <c r="F28" s="94" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G28" s="94" t="s">
         <v>346</v>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="E29" s="56"/>
       <c r="F29" s="94" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G29" s="94" t="s">
         <v>346</v>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="E30" s="56"/>
       <c r="F30" s="94" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G30" s="94" t="s">
         <v>346</v>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="E31" s="56"/>
       <c r="F31" s="94" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G31" s="94" t="s">
         <v>346</v>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="E32" s="56"/>
       <c r="F32" s="94" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G32" s="94" t="s">
         <v>346</v>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="E33" s="56"/>
       <c r="F33" s="94" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G33" s="94" t="s">
         <v>346</v>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="E34" s="56"/>
       <c r="F34" s="94" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G34" s="94" t="s">
         <v>346</v>
@@ -9143,7 +9143,7 @@
       </c>
       <c r="E35" s="56"/>
       <c r="F35" s="94" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G35" s="94" t="s">
         <v>346</v>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="E36" s="56"/>
       <c r="F36" s="94" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G36" s="94" t="s">
         <v>346</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="E37" s="56"/>
       <c r="F37" s="94" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G37" s="94" t="s">
         <v>346</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="E38" s="56"/>
       <c r="F38" s="94" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G38" s="94" t="s">
         <v>346</v>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="E39" s="56"/>
       <c r="F39" s="94" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G39" s="94" t="s">
         <v>346</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="E40" s="56"/>
       <c r="F40" s="94" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G40" s="94" t="s">
         <v>346</v>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="E41" s="56"/>
       <c r="F41" s="94" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G41" s="94" t="s">
         <v>346</v>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="E42" s="56"/>
       <c r="F42" s="94" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G42" s="94" t="s">
         <v>346</v>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="E43" s="56"/>
       <c r="F43" s="94" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G43" s="94" t="s">
         <v>346</v>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="E44" s="56"/>
       <c r="F44" s="94" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G44" s="94" t="s">
         <v>346</v>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="E45" s="56"/>
       <c r="F45" s="94" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G45" s="94" t="s">
         <v>346</v>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="E46" s="56"/>
       <c r="F46" s="94" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G46" s="94" t="s">
         <v>346</v>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="E47" s="56"/>
       <c r="F47" s="94" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G47" s="94" t="s">
         <v>346</v>
@@ -9448,7 +9448,7 @@
         <v>24</v>
       </c>
       <c r="C48" s="117" t="s">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="D48" s="96"/>
       <c r="E48" s="56"/>
@@ -9866,7 +9866,7 @@
         <v>5</v>
       </c>
       <c r="C67" s="79" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D67" s="93">
         <v>2015</v>
